--- a/data/dividends_info_20260604.xlsx
+++ b/data/dividends_info_20260604.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>65.19999694824219</v>
+        <v>66.72000122070312</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1380368162769161</v>
+        <v>0.1348920838629618</v>
       </c>
       <c r="J2" t="n">
         <v>284</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>55.40000152587891</v>
+        <v>55.65000152587891</v>
       </c>
       <c r="I3" t="n">
-        <v>1.263537871335636</v>
+        <v>1.257861600730557</v>
       </c>
       <c r="J3" t="n">
         <v>263</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.079999923706055</v>
+        <v>9.060000419616699</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6607929570941081</v>
+        <v>0.6622516249567504</v>
       </c>
       <c r="J4" t="n">
         <v>193</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>65.19999694824219</v>
+        <v>66.72000122070312</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1380368162769161</v>
+        <v>0.1348920838629618</v>
       </c>
       <c r="J6" t="n">
         <v>193</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.085000038146973</v>
+        <v>2.089999914169312</v>
       </c>
       <c r="I7" t="n">
-        <v>3.693045495981532</v>
+        <v>3.68421067761643</v>
       </c>
       <c r="J7" t="n">
         <v>172</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>23.3799991607666</v>
+        <v>23.41500091552734</v>
       </c>
       <c r="I8" t="n">
-        <v>1.154833232214483</v>
+        <v>1.153106937616873</v>
       </c>
       <c r="J8" t="n">
         <v>172</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.519999980926514</v>
+        <v>5.53000020980835</v>
       </c>
       <c r="I9" t="n">
-        <v>3.623188418316456</v>
+        <v>3.616636390813651</v>
       </c>
       <c r="J9" t="n">
         <v>165</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7.099999904632568</v>
+        <v>7.199999809265137</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8450704338862249</v>
+        <v>0.8333333554091283</v>
       </c>
       <c r="J10" t="n">
         <v>137</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4.96999979019165</v>
+        <v>4.960000038146973</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7645875574279384</v>
+        <v>0.7661290263658259</v>
       </c>
       <c r="J13" t="n">
         <v>116</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>23.38999938964844</v>
+        <v>23.41500091552734</v>
       </c>
       <c r="I14" t="n">
-        <v>1.154339491430223</v>
+        <v>1.153106937616873</v>
       </c>
       <c r="J14" t="n">
         <v>109</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>65.19999694824219</v>
+        <v>66.72000122070312</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1380368162769161</v>
+        <v>0.1348920838629618</v>
       </c>
       <c r="J15" t="n">
         <v>109</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5.960000038146973</v>
+        <v>5.840000152587891</v>
       </c>
       <c r="I16" t="n">
-        <v>5.03355701476259</v>
+        <v>5.136986167150362</v>
       </c>
       <c r="J16" t="n">
         <v>102</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>4.96999979019165</v>
+        <v>4.960000038146973</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7645875574279384</v>
+        <v>0.7661290263658259</v>
       </c>
       <c r="J18" t="n">
         <v>60</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>6</v>
+        <v>5.909999847412109</v>
       </c>
       <c r="I19" t="n">
-        <v>4.166666666666666</v>
+        <v>4.230118552532127</v>
       </c>
       <c r="J19" t="n">
         <v>53</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>4.360000133514404</v>
+        <v>4.340000152587891</v>
       </c>
       <c r="I20" t="n">
-        <v>3.211009075982577</v>
+        <v>3.225806338198391</v>
       </c>
       <c r="J20" t="n">
         <v>46</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>9.569999694824219</v>
+        <v>9.567000389099121</v>
       </c>
       <c r="I21" t="n">
-        <v>2.71682349311481</v>
+        <v>2.717675231792093</v>
       </c>
       <c r="J21" t="n">
         <v>46</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>3.608000040054321</v>
+        <v>3.605999946594238</v>
       </c>
       <c r="I23" t="n">
-        <v>6.097560907917499</v>
+        <v>6.100942963345953</v>
       </c>
       <c r="J23" t="n">
         <v>46</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6.054999828338623</v>
+        <v>6.050000190734863</v>
       </c>
       <c r="I25" t="n">
-        <v>1.651527709909748</v>
+        <v>1.652892509873682</v>
       </c>
       <c r="J25" t="n">
         <v>46</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>18.79999923706055</v>
+        <v>18.54999923706055</v>
       </c>
       <c r="I26" t="n">
-        <v>2.000000081163775</v>
+        <v>2.026954261263794</v>
       </c>
       <c r="J26" t="n">
         <v>46</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>5.820000171661377</v>
+        <v>5.829999923706055</v>
       </c>
       <c r="I27" t="n">
-        <v>2.061855609288493</v>
+        <v>2.058319066387184</v>
       </c>
       <c r="J27" t="n">
         <v>39</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>9.399999618530273</v>
+        <v>9.300000190734863</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5319149152031317</v>
+        <v>0.5376343975757395</v>
       </c>
       <c r="J28" t="n">
         <v>39</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>4.320000171661377</v>
+        <v>4.389999866485596</v>
       </c>
       <c r="I31" t="n">
-        <v>1.620370305982639</v>
+        <v>1.594533078107776</v>
       </c>
       <c r="J31" t="n">
         <v>32</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>34.40000152587891</v>
+        <v>34.5</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4360464922862167</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="J32" t="n">
         <v>32</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>22.60000038146973</v>
+        <v>22.6200008392334</v>
       </c>
       <c r="I34" t="n">
-        <v>4.203539752056497</v>
+        <v>4.199823009521143</v>
       </c>
       <c r="J34" t="n">
         <v>18</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>31.54999923706055</v>
+        <v>31.79999923706055</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6180665759602971</v>
+        <v>0.6132075618817686</v>
       </c>
       <c r="J35" t="n">
         <v>18</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1.850000023841858</v>
+        <v>1.835000038146973</v>
       </c>
       <c r="I36" t="n">
-        <v>1.783783760795287</v>
+        <v>1.798365085230418</v>
       </c>
       <c r="J36" t="n">
         <v>18</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>5.300000190734863</v>
+        <v>5.264999866485596</v>
       </c>
       <c r="I37" t="n">
-        <v>5.471697916293668</v>
+        <v>5.508072314417283</v>
       </c>
       <c r="J37" t="n">
         <v>18</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2.595999956130981</v>
+        <v>2.588000059127808</v>
       </c>
       <c r="I39" t="n">
-        <v>5.338983141069319</v>
+        <v>5.355486740085707</v>
       </c>
       <c r="J39" t="n">
         <v>18</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>50.97000122070312</v>
+        <v>51.2599983215332</v>
       </c>
       <c r="I40" t="n">
-        <v>1.236021159332649</v>
+        <v>1.229028522490901</v>
       </c>
       <c r="J40" t="n">
         <v>18</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>19.14999961853027</v>
+        <v>18.79999923706055</v>
       </c>
       <c r="I42" t="n">
-        <v>4.073107130745016</v>
+        <v>4.148936338584427</v>
       </c>
       <c r="J42" t="n">
         <v>18</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>25.64999961853027</v>
+        <v>25.81999969482422</v>
       </c>
       <c r="I43" t="n">
-        <v>3.313840205229229</v>
+        <v>3.292021727523056</v>
       </c>
       <c r="J43" t="n">
         <v>18</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>65.19999694824219</v>
+        <v>66.72000122070312</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1380368162769161</v>
+        <v>0.1348920838629618</v>
       </c>
       <c r="J44" t="n">
         <v>18</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>6.23799991607666</v>
+        <v>6.210000038146973</v>
       </c>
       <c r="I46" t="n">
-        <v>2.90638028918133</v>
+        <v>2.9194846841595</v>
       </c>
       <c r="J46" t="n">
         <v>18</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>8.789999961853027</v>
+        <v>8.739999771118164</v>
       </c>
       <c r="I47" t="n">
-        <v>2.957906725009692</v>
+        <v>2.974828453190412</v>
       </c>
       <c r="J47" t="n">
         <v>18</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>9.906000137329102</v>
+        <v>9.87600040435791</v>
       </c>
       <c r="I48" t="n">
-        <v>2.79628504098412</v>
+        <v>2.80477914802201</v>
       </c>
       <c r="J48" t="n">
         <v>18</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>3.053999900817871</v>
+        <v>3.01200008392334</v>
       </c>
       <c r="I50" t="n">
-        <v>3.601833777746412</v>
+        <v>3.652058331177646</v>
       </c>
       <c r="J50" t="n">
         <v>11</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>3.140000104904175</v>
+        <v>3.164999961853027</v>
       </c>
       <c r="I52" t="n">
-        <v>5.095541231037086</v>
+        <v>5.055292320013933</v>
       </c>
       <c r="J52" t="n">
         <v>4</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0.8949999809265137</v>
+        <v>0.8799999952316284</v>
       </c>
       <c r="I53" t="n">
-        <v>2.79329614891385</v>
+        <v>2.840909106302853</v>
       </c>
       <c r="J53" t="n">
         <v>4</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>26.60000038146973</v>
+        <v>26.64999961853027</v>
       </c>
       <c r="I54" t="n">
-        <v>4.172932270983183</v>
+        <v>4.165103249112976</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.8849999904632568</v>
+        <v>0.9010000228881836</v>
       </c>
       <c r="I55" t="n">
-        <v>3.389830545003326</v>
+        <v>3.329633655705586</v>
       </c>
       <c r="J55" t="n">
         <v>-3</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0.4740000069141388</v>
+        <v>0.4760000109672546</v>
       </c>
       <c r="I56" t="n">
-        <v>4.8523206043257</v>
+        <v>4.831932661779336</v>
       </c>
       <c r="J56" t="n">
         <v>-3</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>9.319999694824219</v>
+        <v>9.479999542236328</v>
       </c>
       <c r="I58" t="n">
-        <v>2.145922817047604</v>
+        <v>2.109704743222172</v>
       </c>
       <c r="J58" t="n">
         <v>-3</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>2.275000095367432</v>
+        <v>2.309999942779541</v>
       </c>
       <c r="I59" t="n">
-        <v>7.912087580415177</v>
+        <v>7.792207985226717</v>
       </c>
       <c r="J59" t="n">
         <v>-10</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>15.90999984741211</v>
+        <v>16.04000091552734</v>
       </c>
       <c r="I61" t="n">
-        <v>1.571338795711331</v>
+        <v>1.558603402310222</v>
       </c>
       <c r="J61" t="n">
         <v>-10</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>3.779999971389771</v>
+        <v>3.769999980926514</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7936507996578126</v>
+        <v>0.7957559721957136</v>
       </c>
       <c r="J62" t="n">
         <v>-10</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>12.69999980926514</v>
+        <v>12.75</v>
       </c>
       <c r="I64" t="n">
-        <v>4.566929202446662</v>
+        <v>4.549019607843137</v>
       </c>
       <c r="J64" t="n">
         <v>-10</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>2.223000049591064</v>
+        <v>2.220999956130981</v>
       </c>
       <c r="I65" t="n">
-        <v>4.678362468733704</v>
+        <v>4.682575508968929</v>
       </c>
       <c r="J65" t="n">
         <v>-17</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>10.44499969482422</v>
+        <v>10.53499984741211</v>
       </c>
       <c r="I66" t="n">
-        <v>2.776448142393943</v>
+        <v>2.752729038446428</v>
       </c>
       <c r="J66" t="n">
         <v>-17</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>2.085000038146973</v>
+        <v>2.089999914169312</v>
       </c>
       <c r="I67" t="n">
-        <v>3.693045495981532</v>
+        <v>3.68421067761643</v>
       </c>
       <c r="J67" t="n">
         <v>-17</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>38.86000061035156</v>
+        <v>38.72000122070312</v>
       </c>
       <c r="I68" t="n">
-        <v>4.220277854455656</v>
+        <v>4.235537056551308</v>
       </c>
       <c r="J68" t="n">
         <v>-17</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>34.56999969482422</v>
+        <v>34.79000091552734</v>
       </c>
       <c r="I69" t="n">
-        <v>5.785363082602045</v>
+        <v>5.748778233309467</v>
       </c>
       <c r="J69" t="n">
         <v>-17</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>3.345999956130981</v>
+        <v>3.263999938964844</v>
       </c>
       <c r="I70" t="n">
-        <v>2.988643195190928</v>
+        <v>3.063725547486203</v>
       </c>
       <c r="J70" t="n">
         <v>-17</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>37.18000030517578</v>
+        <v>38.02999877929688</v>
       </c>
       <c r="I71" t="n">
-        <v>0.3993006960232141</v>
+        <v>0.3903760314628778</v>
       </c>
       <c r="J71" t="n">
         <v>-17</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>19.95000076293945</v>
+        <v>20.04000091552734</v>
       </c>
       <c r="I72" t="n">
-        <v>4.61152864569839</v>
+        <v>4.590818153541939</v>
       </c>
       <c r="J72" t="n">
         <v>-17</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>11.76000022888184</v>
+        <v>11.46000003814697</v>
       </c>
       <c r="I73" t="n">
-        <v>2.551020358513416</v>
+        <v>2.617801038406529</v>
       </c>
       <c r="J73" t="n">
         <v>-17</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>82.55999755859375</v>
+        <v>83.09999847412109</v>
       </c>
       <c r="I74" t="n">
-        <v>1.259689959731286</v>
+        <v>1.251504234773092</v>
       </c>
       <c r="J74" t="n">
         <v>-17</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>44.0099983215332</v>
+        <v>44.04999923706055</v>
       </c>
       <c r="I75" t="n">
-        <v>1.590547663478333</v>
+        <v>1.589103319236995</v>
       </c>
       <c r="J75" t="n">
         <v>-17</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>55.29999923706055</v>
+        <v>55.65000152587891</v>
       </c>
       <c r="I76" t="n">
-        <v>3.978300235717942</v>
+        <v>3.953279316581752</v>
       </c>
       <c r="J76" t="n">
         <v>-17</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>8.788999557495117</v>
+        <v>8.871999740600586</v>
       </c>
       <c r="I77" t="n">
-        <v>9.784958963464799</v>
+        <v>9.693417776653167</v>
       </c>
       <c r="J77" t="n">
         <v>-17</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>11.5600004196167</v>
+        <v>11.67199993133545</v>
       </c>
       <c r="I78" t="n">
-        <v>4.844290481596438</v>
+        <v>4.797806745154151</v>
       </c>
       <c r="J78" t="n">
         <v>-17</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>2.170000076293945</v>
+        <v>2.160000085830688</v>
       </c>
       <c r="I79" t="n">
-        <v>1.843317907541938</v>
+        <v>1.851851778265873</v>
       </c>
       <c r="J79" t="n">
         <v>-17</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>8.729999542236328</v>
+        <v>8.600000381469727</v>
       </c>
       <c r="I80" t="n">
-        <v>3.43642629702991</v>
+        <v>3.488371938289734</v>
       </c>
       <c r="J80" t="n">
         <v>-17</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>90.40000152587891</v>
+        <v>89.69999694824219</v>
       </c>
       <c r="I82" t="n">
-        <v>2.278761023483259</v>
+        <v>2.296544113807095</v>
       </c>
       <c r="J82" t="n">
         <v>-17</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>15.06999969482422</v>
+        <v>15.11999988555908</v>
       </c>
       <c r="I83" t="n">
-        <v>4.976775150550182</v>
+        <v>4.960317497861329</v>
       </c>
       <c r="J83" t="n">
         <v>-17</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>14.02000045776367</v>
+        <v>13.94999980926514</v>
       </c>
       <c r="I84" t="n">
-        <v>2.139800215440599</v>
+        <v>2.150537663812366</v>
       </c>
       <c r="J84" t="n">
         <v>-17</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>51.20000076293945</v>
+        <v>51</v>
       </c>
       <c r="I85" t="n">
-        <v>1.660156225261745</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="J85" t="n">
         <v>-17</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>35.15999984741211</v>
+        <v>35.43999862670898</v>
       </c>
       <c r="I86" t="n">
-        <v>2.417519919479075</v>
+        <v>2.398419957497985</v>
       </c>
       <c r="J86" t="n">
         <v>-17</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>68.33999633789062</v>
+        <v>72.09999847412109</v>
       </c>
       <c r="I87" t="n">
-        <v>1.902253540624239</v>
+        <v>1.803051355773066</v>
       </c>
       <c r="J87" t="n">
         <v>-17</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>5.519999980926514</v>
+        <v>5.53000020980835</v>
       </c>
       <c r="I90" t="n">
-        <v>3.623188418316456</v>
+        <v>3.616636390813651</v>
       </c>
       <c r="J90" t="n">
         <v>-17</v>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>23.29999923706055</v>
+        <v>23.26000022888184</v>
       </c>
       <c r="I91" t="n">
-        <v>4.291845634095209</v>
+        <v>4.299226096989907</v>
       </c>
       <c r="J91" t="n">
         <v>-17</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>4.789999961853027</v>
+        <v>4.860000133514404</v>
       </c>
       <c r="I92" t="n">
-        <v>4.488517781048719</v>
+        <v>4.423868191224254</v>
       </c>
       <c r="J92" t="n">
         <v>-17</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>23.38999938964844</v>
+        <v>23.41500091552734</v>
       </c>
       <c r="I93" t="n">
-        <v>1.154339491430223</v>
+        <v>1.153106937616873</v>
       </c>
       <c r="J93" t="n">
         <v>-17</v>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>8.564999580383301</v>
+        <v>8.520000457763672</v>
       </c>
       <c r="I95" t="n">
-        <v>2.802101713462775</v>
+        <v>2.816901257103866</v>
       </c>
       <c r="J95" t="n">
         <v>-17</v>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>20.47999954223633</v>
+        <v>20.89999961853027</v>
       </c>
       <c r="I96" t="n">
-        <v>3.8574219612201</v>
+        <v>3.779904375211439</v>
       </c>
       <c r="J96" t="n">
         <v>-17</v>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>7.099999904632568</v>
+        <v>7.199999809265137</v>
       </c>
       <c r="I98" t="n">
-        <v>0.8450704338862249</v>
+        <v>0.8333333554091283</v>
       </c>
       <c r="J98" t="n">
         <v>-17</v>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>34.91999816894531</v>
+        <v>35.04000091552734</v>
       </c>
       <c r="I99" t="n">
-        <v>1.00229100330039</v>
+        <v>0.9988584213903482</v>
       </c>
       <c r="J99" t="n">
         <v>-17</v>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>6.554999828338623</v>
+        <v>6.505000114440918</v>
       </c>
       <c r="I100" t="n">
-        <v>8.45614057232536</v>
+        <v>8.521137436561601</v>
       </c>
       <c r="J100" t="n">
         <v>-17</v>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>2.279999971389771</v>
+        <v>2.259999990463257</v>
       </c>
       <c r="I101" t="n">
-        <v>2.631578980390385</v>
+        <v>2.654867267840171</v>
       </c>
       <c r="J101" t="n">
         <v>-17</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>13.10000038146973</v>
+        <v>13.19999980926514</v>
       </c>
       <c r="I102" t="n">
-        <v>1.526717512794159</v>
+        <v>1.515151537044865</v>
       </c>
       <c r="J102" t="n">
         <v>-17</v>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>7.235000133514404</v>
+        <v>7.239999771118164</v>
       </c>
       <c r="I103" t="n">
-        <v>1.42363508084647</v>
+        <v>1.422651978676685</v>
       </c>
       <c r="J103" t="n">
         <v>-17</v>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>5.657000064849854</v>
+        <v>5.690000057220459</v>
       </c>
       <c r="I104" t="n">
-        <v>3.35867063499924</v>
+        <v>3.33919153056765</v>
       </c>
       <c r="J104" t="n">
         <v>-17</v>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>9.954000473022461</v>
+        <v>10.02999973297119</v>
       </c>
       <c r="I105" t="n">
-        <v>4.339963627395994</v>
+        <v>4.307078878376285</v>
       </c>
       <c r="J105" t="n">
         <v>-17</v>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>26.10000038146973</v>
+        <v>25.86000061035156</v>
       </c>
       <c r="I106" t="n">
-        <v>1.685823730149781</v>
+        <v>1.701469410731071</v>
       </c>
       <c r="J106" t="n">
         <v>-17</v>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>7</v>
+        <v>6.869999885559082</v>
       </c>
       <c r="I108" t="n">
-        <v>6.714285714285714</v>
+        <v>6.841339269713122</v>
       </c>
       <c r="J108" t="n">
         <v>-17</v>
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>53.84000015258789</v>
+        <v>53.5</v>
       </c>
       <c r="I109" t="n">
-        <v>2.600297169450708</v>
+        <v>2.616822429906542</v>
       </c>
       <c r="J109" t="n">
         <v>-17</v>
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>3.430000066757202</v>
+        <v>3.371999979019165</v>
       </c>
       <c r="I110" t="n">
-        <v>8.746355514903142</v>
+        <v>8.896797208381445</v>
       </c>
       <c r="J110" t="n">
         <v>-17</v>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>15.80000019073486</v>
+        <v>15.89999961853027</v>
       </c>
       <c r="I111" t="n">
-        <v>0.7594936617175999</v>
+        <v>0.7547169992390997</v>
       </c>
       <c r="J111" t="n">
         <v>-17</v>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>3.349999904632568</v>
+        <v>3.440000057220459</v>
       </c>
       <c r="I112" t="n">
-        <v>5.074627010135566</v>
+        <v>4.941860382914093</v>
       </c>
       <c r="J112" t="n">
         <v>-17</v>
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>22.5</v>
+        <v>22.54999923706055</v>
       </c>
       <c r="I113" t="n">
-        <v>3.111111111111111</v>
+        <v>3.104212965335988</v>
       </c>
       <c r="J113" t="n">
         <v>-17</v>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>2.420000076293945</v>
+        <v>2.519999980926514</v>
       </c>
       <c r="I114" t="n">
-        <v>1.446280946139471</v>
+        <v>1.388888899401172</v>
       </c>
       <c r="J114" t="n">
         <v>-17</v>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>5.559999942779541</v>
+        <v>5.550000190734863</v>
       </c>
       <c r="I115" t="n">
-        <v>5.935251859643496</v>
+        <v>5.945945741603757</v>
       </c>
       <c r="J115" t="n">
         <v>-17</v>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>0.878000020980835</v>
+        <v>0.890999972820282</v>
       </c>
       <c r="I116" t="n">
-        <v>7.972664957547646</v>
+        <v>7.85634142933013</v>
       </c>
       <c r="J116" t="n">
         <v>-17</v>
@@ -5928,10 +5928,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>50.84999847412109</v>
+        <v>50.65000152587891</v>
       </c>
       <c r="I117" t="n">
-        <v>1.396263562055637</v>
+        <v>1.401776858066303</v>
       </c>
       <c r="J117" t="n">
         <v>-17</v>
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>105.4000015258789</v>
+        <v>106.0999984741211</v>
       </c>
       <c r="I118" t="n">
-        <v>1.280834896068321</v>
+        <v>1.272384561182891</v>
       </c>
       <c r="J118" t="n">
         <v>-17</v>
@@ -6022,10 +6022,10 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>7.699999809265137</v>
+        <v>7.760000228881836</v>
       </c>
       <c r="I119" t="n">
-        <v>1.038961064696896</v>
+        <v>1.030927804644246</v>
       </c>
       <c r="J119" t="n">
         <v>-17</v>
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>4.270999908447266</v>
+        <v>4.328999996185303</v>
       </c>
       <c r="I121" t="n">
-        <v>3.980332560152267</v>
+        <v>3.927003930464387</v>
       </c>
       <c r="J121" t="n">
         <v>-17</v>
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>57.70000076293945</v>
+        <v>58.29999923706055</v>
       </c>
       <c r="I123" t="n">
-        <v>0.7798960035526269</v>
+        <v>0.771869649895194</v>
       </c>
       <c r="J123" t="n">
         <v>-17</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>5.820000171661377</v>
+        <v>5.78000020980835</v>
       </c>
       <c r="I124" t="n">
-        <v>0.6872852030961643</v>
+        <v>0.6920414973709197</v>
       </c>
       <c r="J124" t="n">
         <v>-17</v>
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>38.2599983215332</v>
+        <v>38.29999923706055</v>
       </c>
       <c r="I125" t="n">
-        <v>2.744380674499526</v>
+        <v>2.74151441492453</v>
       </c>
       <c r="J125" t="n">
         <v>-17</v>
@@ -6351,10 +6351,10 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>1.5</v>
+        <v>1.600000023841858</v>
       </c>
       <c r="I126" t="n">
-        <v>3.333333333333333</v>
+        <v>3.124999953433872</v>
       </c>
       <c r="J126" t="n">
         <v>-17</v>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>17.63999938964844</v>
+        <v>17.84000015258789</v>
       </c>
       <c r="I127" t="n">
-        <v>2.154195085873942</v>
+        <v>2.130044824830771</v>
       </c>
       <c r="J127" t="n">
         <v>-17</v>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>27.13999938964844</v>
+        <v>27.3799991607666</v>
       </c>
       <c r="I128" t="n">
-        <v>2.210759076983797</v>
+        <v>2.191380636927678</v>
       </c>
       <c r="J128" t="n">
         <v>-17</v>
@@ -6492,10 +6492,10 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>37.25</v>
+        <v>37.29999923706055</v>
       </c>
       <c r="I129" t="n">
-        <v>0.9395973154362416</v>
+        <v>0.938337820801473</v>
       </c>
       <c r="J129" t="n">
         <v>-17</v>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>20.76000022888184</v>
+        <v>20.67000007629395</v>
       </c>
       <c r="I132" t="n">
-        <v>5.394990306608127</v>
+        <v>5.418480870179136</v>
       </c>
       <c r="J132" t="n">
         <v>-17</v>
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>1.399999976158142</v>
+        <v>1.460000038146973</v>
       </c>
       <c r="I133" t="n">
-        <v>7.142857264499278</v>
+        <v>6.849314889533817</v>
       </c>
       <c r="J133" t="n">
         <v>-17</v>
@@ -6727,10 +6727,10 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>9.199999809265137</v>
+        <v>9.119999885559082</v>
       </c>
       <c r="I134" t="n">
-        <v>2.826087015112318</v>
+        <v>2.850877228756251</v>
       </c>
       <c r="J134" t="n">
         <v>-17</v>
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>2.186000108718872</v>
+        <v>2.232000112533569</v>
       </c>
       <c r="I135" t="n">
-        <v>4.222323669237755</v>
+        <v>4.135304451003329</v>
       </c>
       <c r="J135" t="n">
         <v>-17</v>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>9.079999923706055</v>
+        <v>9.180000305175781</v>
       </c>
       <c r="I136" t="n">
-        <v>3.854625583048964</v>
+        <v>3.812636038831788</v>
       </c>
       <c r="J136" t="n">
         <v>-24</v>
@@ -6868,10 +6868,10 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>6.800000190734863</v>
+        <v>6.5</v>
       </c>
       <c r="I137" t="n">
-        <v>1.41176466628342</v>
+        <v>1.476923076923077</v>
       </c>
       <c r="J137" t="n">
         <v>-24</v>
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>9.079999923706055</v>
+        <v>9.060000419616699</v>
       </c>
       <c r="I140" t="n">
-        <v>0.6607929570941081</v>
+        <v>0.6622516249567504</v>
       </c>
       <c r="J140" t="n">
         <v>-24</v>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>18.71999931335449</v>
+        <v>18.70000076293945</v>
       </c>
       <c r="I141" t="n">
-        <v>2.670940268909676</v>
+        <v>2.673796682355883</v>
       </c>
       <c r="J141" t="n">
         <v>-24</v>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>15.11999988555908</v>
+        <v>15.14000034332275</v>
       </c>
       <c r="I143" t="n">
-        <v>3.306878331907552</v>
+        <v>3.30250983264024</v>
       </c>
       <c r="J143" t="n">
         <v>-24</v>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>3.150000095367432</v>
+        <v>3.190000057220459</v>
       </c>
       <c r="I145" t="n">
-        <v>3.492063386339963</v>
+        <v>3.448275800215698</v>
       </c>
       <c r="J145" t="n">
         <v>-24</v>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>4.909999847412109</v>
+        <v>4.840000152587891</v>
       </c>
       <c r="I147" t="n">
-        <v>1.934826944038933</v>
+        <v>1.962809855474997</v>
       </c>
       <c r="J147" t="n">
         <v>-24</v>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>8.199999809265137</v>
+        <v>8.350000381469727</v>
       </c>
       <c r="I149" t="n">
-        <v>1.097561001139408</v>
+        <v>1.077844262135933</v>
       </c>
       <c r="J149" t="n">
         <v>-24</v>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>7.090000152587891</v>
+        <v>7.010000228881836</v>
       </c>
       <c r="I151" t="n">
-        <v>3.102961851414047</v>
+        <v>3.138373649312878</v>
       </c>
       <c r="J151" t="n">
         <v>-24</v>
@@ -9395,44 +9395,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>OPS ECOM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>